--- a/data/branch_weight_data_sensitivity.xlsx
+++ b/data/branch_weight_data_sensitivity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\McGrath\occ-coseismic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F9F8A5-E48E-43D1-9529-5EAECF3BEA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DAA886-632D-4FF2-B1BB-3BF64D8F8202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30810" yWindow="1725" windowWidth="28800" windowHeight="15600" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all sheets" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="346">
   <si>
     <t>N</t>
   </si>
@@ -904,6 +904,180 @@
   </si>
   <si>
     <t>_sz_fq_plhb110</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_full</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_3e10_nolocking_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_narchi10_sense</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_3e10_nolocking_uniformSlip_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_narchi10_sense</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_prem_locking_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_narchi10_sense</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_prem_nolocking_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_narchi10_sense</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_prem_nolocking_uniformSlip_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_narchi10_sense</t>
+  </si>
+  <si>
+    <t>_sz_fq_3nhb110_full</t>
+  </si>
+  <si>
+    <t>_sz_fq_3nub110_full</t>
+  </si>
+  <si>
+    <t>_sz_fq_plhb110_full</t>
+  </si>
+  <si>
+    <t>_sz_fq_pnhb110_full</t>
+  </si>
+  <si>
+    <t>_sz_fq_pnub110_full</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_narchi10_sense</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_full_n0</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_archi0</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_archi1</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_full_n1</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_full_n2</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_archi2</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_full_n3</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_archi3</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_full_n4</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_archi4</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_full_n5</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_archi5</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_full_n6</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_archi6</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_full_n7</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_archi7</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_full_n8</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_archi8</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_full_n9</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_nIt500000_archi9</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_n0</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_n1</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_archi0</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_archi1</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_n2</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_archi2</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_n3</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_archi3</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_n4</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_archi4</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_n5</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_archi5</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_n6</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_archi6</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_n7</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_archi7</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_n8</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_archi8</t>
+  </si>
+  <si>
+    <t>_sz_fq_3lhb110_n9</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_3e10_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_archi9</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_wuatom_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_narchi10</t>
+  </si>
+  <si>
+    <t>_sz_fq_anhb110</t>
+  </si>
+  <si>
+    <t>_sz_fq_anub110</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_lock_wuatom_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_narchi10_uniformSlip</t>
+  </si>
+  <si>
+    <t>sz_solutions/FQ_hk_noMeanSlip_wuatom_n5000_S10_N1_GR500_nr1-7_taper9-5Mw_alphas1-0_b1-1_pMax6233_nIt500000_narchi10</t>
+  </si>
+  <si>
+    <t>_sz_fq_alhb110</t>
   </si>
 </sst>
 </file>
@@ -7256,7 +7430,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C3AB27-DA22-46B6-9275-CBA251195A6D}">
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -7265,7 +7439,7 @@
     <col min="8" max="11" width="12.5703125" customWidth="1"/>
     <col min="12" max="12" width="15.28515625" customWidth="1"/>
     <col min="13" max="13" width="15.140625" customWidth="1"/>
-    <col min="14" max="14" width="19" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
     <col min="15" max="15" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7358,12 +7532,12 @@
         <v>1.27536454442839E-4</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L8" si="0">K2*J2</f>
+        <f t="shared" ref="L2:L5" si="0">K2*J2</f>
         <v>1.0631412059699625E-5</v>
       </c>
       <c r="M2">
-        <f t="shared" ref="M2:M19" si="1">L2/(SUM(L$2:L$22))</f>
-        <v>0.21006012368807689</v>
+        <f t="shared" ref="M2:M7" si="1">L2/(SUM(L$2:L$22))</f>
+        <v>5.3992521239724249E-2</v>
       </c>
       <c r="N2" t="s">
         <v>286</v>
@@ -7383,7 +7557,7 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>0.42</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
         <v>282</v>
@@ -7401,7 +7575,7 @@
         <v>0.255</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J19" si="2">PRODUCT(G3:I3)</f>
+        <f t="shared" ref="J3:J7" si="2">PRODUCT(G3:I3)</f>
         <v>4.3648349999999995E-2</v>
       </c>
       <c r="K3">
@@ -7413,7 +7587,7 @@
       </c>
       <c r="M3">
         <f t="shared" si="1"/>
-        <v>0.10999041384077948</v>
+        <v>2.8271238020800168E-2</v>
       </c>
       <c r="N3" t="s">
         <v>284</v>
@@ -7433,7 +7607,7 @@
         <v>4</v>
       </c>
       <c r="D4">
-        <v>1.58</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>282</v>
@@ -7463,7 +7637,7 @@
       </c>
       <c r="M4">
         <f t="shared" si="1"/>
-        <v>0.1108530837532562</v>
+        <v>2.8492973220963311E-2</v>
       </c>
       <c r="N4" t="s">
         <v>281</v>
@@ -7513,7 +7687,7 @@
       </c>
       <c r="M5">
         <f t="shared" si="1"/>
-        <v>0.27742736379941052</v>
+        <v>7.1308169153813522E-2</v>
       </c>
       <c r="N5" t="s">
         <v>287</v>
@@ -7533,7 +7707,7 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>0.42</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>282</v>
@@ -7558,12 +7732,12 @@
         <v>1.27536454442839E-4</v>
       </c>
       <c r="L6">
-        <f t="shared" ref="L6:L7" si="5">K6*J6</f>
+        <f t="shared" ref="L6:L11" si="5">K6*J6</f>
         <v>7.3520397862732014E-6</v>
       </c>
       <c r="M6">
         <f t="shared" si="1"/>
-        <v>0.14526484141447576</v>
+        <v>3.7337953047684704E-2</v>
       </c>
       <c r="N6" t="s">
         <v>285</v>
@@ -7583,7 +7757,7 @@
         <v>4</v>
       </c>
       <c r="D7">
-        <v>1.58</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
         <v>282</v>
@@ -7613,13 +7787,1463 @@
       </c>
       <c r="M7">
         <f t="shared" si="1"/>
-        <v>0.14640417350400106</v>
+        <v>3.7630799738254783E-2</v>
       </c>
       <c r="N7" t="s">
         <v>283</v>
       </c>
       <c r="O7" t="s">
         <v>280</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>21.5</v>
+      </c>
+      <c r="B8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G8">
+        <v>0.5</v>
+      </c>
+      <c r="H8">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I8">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J8">
+        <f>PRODUCT(G8:I8)</f>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K8">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="5"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M8">
+        <f t="shared" ref="M8:M13" si="6">L8/(SUM(L$2:L$22))</f>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N8" t="s">
+        <v>288</v>
+      </c>
+      <c r="O8" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>21.5</v>
+      </c>
+      <c r="B9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>282</v>
+      </c>
+      <c r="F9" t="s">
+        <v>260</v>
+      </c>
+      <c r="G9">
+        <v>0.5</v>
+      </c>
+      <c r="H9">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I9">
+        <v>0.255</v>
+      </c>
+      <c r="J9">
+        <f t="shared" ref="J9:J13" si="7">PRODUCT(G9:I9)</f>
+        <v>4.3648349999999995E-2</v>
+      </c>
+      <c r="K9">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="5"/>
+        <v>5.5667558012800908E-6</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="6"/>
+        <v>2.8271238020800168E-2</v>
+      </c>
+      <c r="N9" t="s">
+        <v>294</v>
+      </c>
+      <c r="O9" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>21.5</v>
+      </c>
+      <c r="B10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>282</v>
+      </c>
+      <c r="F10" t="s">
+        <v>260</v>
+      </c>
+      <c r="G10">
+        <v>0.5</v>
+      </c>
+      <c r="H10">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I10">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="7"/>
+        <v>4.3990689999999999E-2</v>
+      </c>
+      <c r="K10">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="5"/>
+        <v>5.6104166310940532E-6</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="6"/>
+        <v>2.8492973220963311E-2</v>
+      </c>
+      <c r="N10" t="s">
+        <v>295</v>
+      </c>
+      <c r="O10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>21.5</v>
+      </c>
+      <c r="B11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>282</v>
+      </c>
+      <c r="F11" t="s">
+        <v>260</v>
+      </c>
+      <c r="G11">
+        <v>0.5</v>
+      </c>
+      <c r="H11">
+        <v>0.45212999999999998</v>
+      </c>
+      <c r="I11">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="7"/>
+        <v>0.11009365499999998</v>
+      </c>
+      <c r="K11">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="5"/>
+        <v>1.4040954415353132E-5</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="6"/>
+        <v>7.1308169153813522E-2</v>
+      </c>
+      <c r="N11" t="s">
+        <v>296</v>
+      </c>
+      <c r="O11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>21.5</v>
+      </c>
+      <c r="B12">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F12" t="s">
+        <v>260</v>
+      </c>
+      <c r="G12">
+        <v>0.5</v>
+      </c>
+      <c r="H12">
+        <v>0.45212999999999998</v>
+      </c>
+      <c r="I12">
+        <v>0.255</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="7"/>
+        <v>5.7646574999999999E-2</v>
+      </c>
+      <c r="K12">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L12">
+        <f t="shared" ref="L12:L14" si="8">K12*J12</f>
+        <v>7.3520397862732014E-6</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="6"/>
+        <v>3.7337953047684704E-2</v>
+      </c>
+      <c r="N12" t="s">
+        <v>297</v>
+      </c>
+      <c r="O12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>21.5</v>
+      </c>
+      <c r="B13">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>282</v>
+      </c>
+      <c r="F13" t="s">
+        <v>260</v>
+      </c>
+      <c r="G13">
+        <v>0.5</v>
+      </c>
+      <c r="H13">
+        <v>0.45212999999999998</v>
+      </c>
+      <c r="I13">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="7"/>
+        <v>5.8098705E-2</v>
+      </c>
+      <c r="K13">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="8"/>
+        <v>7.4097028434204424E-6</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="6"/>
+        <v>3.7630799738254783E-2</v>
+      </c>
+      <c r="N13" t="s">
+        <v>298</v>
+      </c>
+      <c r="O13" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>21.5</v>
+      </c>
+      <c r="B14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>282</v>
+      </c>
+      <c r="F14" t="s">
+        <v>260</v>
+      </c>
+      <c r="G14">
+        <v>0.5</v>
+      </c>
+      <c r="H14">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I14">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J14">
+        <f>PRODUCT(G14:I14)</f>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K14">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="8"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M14">
+        <f t="shared" ref="M14" si="9">L14/(SUM(L$2:L$22))</f>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N14" t="s">
+        <v>300</v>
+      </c>
+      <c r="O14" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>21.5</v>
+      </c>
+      <c r="B15">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>282</v>
+      </c>
+      <c r="F15" t="s">
+        <v>260</v>
+      </c>
+      <c r="G15">
+        <v>0.5</v>
+      </c>
+      <c r="H15">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I15">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J15">
+        <f>PRODUCT(G15:I15)</f>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K15">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L15">
+        <f t="shared" ref="L15:L16" si="10">K15*J15</f>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M15">
+        <f t="shared" ref="M15:M16" si="11">L15/(SUM(L$2:L$22))</f>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N15" t="s">
+        <v>303</v>
+      </c>
+      <c r="O15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>21.5</v>
+      </c>
+      <c r="B16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>282</v>
+      </c>
+      <c r="F16" t="s">
+        <v>260</v>
+      </c>
+      <c r="G16">
+        <v>0.5</v>
+      </c>
+      <c r="H16">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I16">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J16">
+        <f t="shared" ref="J16:J23" si="12">PRODUCT(G16:I16)</f>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K16">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="10"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="11"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N16" t="s">
+        <v>304</v>
+      </c>
+      <c r="O16" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>21.5</v>
+      </c>
+      <c r="B17">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>282</v>
+      </c>
+      <c r="F17" t="s">
+        <v>260</v>
+      </c>
+      <c r="G17">
+        <v>0.5</v>
+      </c>
+      <c r="H17">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I17">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="12"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K17">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L17">
+        <f t="shared" ref="L17:L25" si="13">K17*J17</f>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M17">
+        <f t="shared" ref="M17:M25" si="14">L17/(SUM(L$2:L$22))</f>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N17" t="s">
+        <v>306</v>
+      </c>
+      <c r="O17" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>21.5</v>
+      </c>
+      <c r="B18">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>282</v>
+      </c>
+      <c r="F18" t="s">
+        <v>260</v>
+      </c>
+      <c r="G18">
+        <v>0.5</v>
+      </c>
+      <c r="H18">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I18">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="12"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K18">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="13"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="14"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N18" t="s">
+        <v>308</v>
+      </c>
+      <c r="O18" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>21.5</v>
+      </c>
+      <c r="B19">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>282</v>
+      </c>
+      <c r="F19" t="s">
+        <v>260</v>
+      </c>
+      <c r="G19">
+        <v>0.5</v>
+      </c>
+      <c r="H19">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I19">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="12"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K19">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="13"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="14"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N19" t="s">
+        <v>310</v>
+      </c>
+      <c r="O19" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>21.5</v>
+      </c>
+      <c r="B20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>282</v>
+      </c>
+      <c r="F20" t="s">
+        <v>260</v>
+      </c>
+      <c r="G20">
+        <v>0.5</v>
+      </c>
+      <c r="H20">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I20">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="12"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K20">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="13"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="14"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N20" t="s">
+        <v>312</v>
+      </c>
+      <c r="O20" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>21.5</v>
+      </c>
+      <c r="B21">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>282</v>
+      </c>
+      <c r="F21" t="s">
+        <v>260</v>
+      </c>
+      <c r="G21">
+        <v>0.5</v>
+      </c>
+      <c r="H21">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I21">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="12"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K21">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="13"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="14"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N21" t="s">
+        <v>314</v>
+      </c>
+      <c r="O21" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21.5</v>
+      </c>
+      <c r="B22">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>282</v>
+      </c>
+      <c r="F22" t="s">
+        <v>260</v>
+      </c>
+      <c r="G22">
+        <v>0.5</v>
+      </c>
+      <c r="H22">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I22">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="12"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K22">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="13"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="14"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N22" t="s">
+        <v>316</v>
+      </c>
+      <c r="O22" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>21.5</v>
+      </c>
+      <c r="B23">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>282</v>
+      </c>
+      <c r="F23" t="s">
+        <v>260</v>
+      </c>
+      <c r="G23">
+        <v>0.5</v>
+      </c>
+      <c r="H23">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I23">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="12"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K23">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="13"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="14"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N23" t="s">
+        <v>318</v>
+      </c>
+      <c r="O23" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>21.5</v>
+      </c>
+      <c r="B24">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>282</v>
+      </c>
+      <c r="F24" t="s">
+        <v>260</v>
+      </c>
+      <c r="G24">
+        <v>0.5</v>
+      </c>
+      <c r="H24">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I24">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J24">
+        <f>PRODUCT(G24:I24)</f>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K24">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="13"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="14"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N24" t="s">
+        <v>320</v>
+      </c>
+      <c r="O24" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>21.5</v>
+      </c>
+      <c r="B25">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>282</v>
+      </c>
+      <c r="F25" t="s">
+        <v>260</v>
+      </c>
+      <c r="G25">
+        <v>0.5</v>
+      </c>
+      <c r="H25">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I25">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J25">
+        <f>PRODUCT(G25:I25)</f>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K25">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="13"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="14"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N25" t="s">
+        <v>321</v>
+      </c>
+      <c r="O25" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>21.5</v>
+      </c>
+      <c r="B26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>282</v>
+      </c>
+      <c r="F26" t="s">
+        <v>260</v>
+      </c>
+      <c r="G26">
+        <v>0.5</v>
+      </c>
+      <c r="H26">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I26">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J26">
+        <f t="shared" ref="J26:J34" si="15">PRODUCT(G26:I26)</f>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K26">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L26">
+        <f t="shared" ref="L26:L34" si="16">K26*J26</f>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M26">
+        <f t="shared" ref="M26:M34" si="17">L26/(SUM(L$2:L$22))</f>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N26" t="s">
+        <v>324</v>
+      </c>
+      <c r="O26" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>21.5</v>
+      </c>
+      <c r="B27">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>282</v>
+      </c>
+      <c r="F27" t="s">
+        <v>260</v>
+      </c>
+      <c r="G27">
+        <v>0.5</v>
+      </c>
+      <c r="H27">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I27">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="15"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K27">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="16"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="17"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N27" t="s">
+        <v>326</v>
+      </c>
+      <c r="O27" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>21.5</v>
+      </c>
+      <c r="B28">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>282</v>
+      </c>
+      <c r="F28" t="s">
+        <v>260</v>
+      </c>
+      <c r="G28">
+        <v>0.5</v>
+      </c>
+      <c r="H28">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I28">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="15"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K28">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="16"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="17"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N28" t="s">
+        <v>328</v>
+      </c>
+      <c r="O28" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>21.5</v>
+      </c>
+      <c r="B29">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>282</v>
+      </c>
+      <c r="F29" t="s">
+        <v>260</v>
+      </c>
+      <c r="G29">
+        <v>0.5</v>
+      </c>
+      <c r="H29">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I29">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="15"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K29">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="16"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="17"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N29" t="s">
+        <v>330</v>
+      </c>
+      <c r="O29" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>21.5</v>
+      </c>
+      <c r="B30">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>282</v>
+      </c>
+      <c r="F30" t="s">
+        <v>260</v>
+      </c>
+      <c r="G30">
+        <v>0.5</v>
+      </c>
+      <c r="H30">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I30">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="15"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K30">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="16"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="17"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N30" t="s">
+        <v>332</v>
+      </c>
+      <c r="O30" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>21.5</v>
+      </c>
+      <c r="B31">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C31">
+        <v>4</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>282</v>
+      </c>
+      <c r="F31" t="s">
+        <v>260</v>
+      </c>
+      <c r="G31">
+        <v>0.5</v>
+      </c>
+      <c r="H31">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I31">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="15"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K31">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="16"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="17"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N31" t="s">
+        <v>334</v>
+      </c>
+      <c r="O31" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>21.5</v>
+      </c>
+      <c r="B32">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C32">
+        <v>4</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>282</v>
+      </c>
+      <c r="F32" t="s">
+        <v>260</v>
+      </c>
+      <c r="G32">
+        <v>0.5</v>
+      </c>
+      <c r="H32">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I32">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="15"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K32">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="16"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="17"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N32" t="s">
+        <v>336</v>
+      </c>
+      <c r="O32" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>21.5</v>
+      </c>
+      <c r="B33">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C33">
+        <v>4</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>282</v>
+      </c>
+      <c r="F33" t="s">
+        <v>260</v>
+      </c>
+      <c r="G33">
+        <v>0.5</v>
+      </c>
+      <c r="H33">
+        <v>0.34233999999999998</v>
+      </c>
+      <c r="I33">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="15"/>
+        <v>8.3359789999999989E-2</v>
+      </c>
+      <c r="K33">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="16"/>
+        <v>1.0631412059699625E-5</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="17"/>
+        <v>5.3992521239724249E-2</v>
+      </c>
+      <c r="N33" t="s">
+        <v>338</v>
+      </c>
+      <c r="O33" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>21.5</v>
+      </c>
+      <c r="B34">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>282</v>
+      </c>
+      <c r="F34" t="s">
+        <v>260</v>
+      </c>
+      <c r="G34">
+        <v>0.5</v>
+      </c>
+      <c r="H34">
+        <v>0.45212999999999998</v>
+      </c>
+      <c r="I34">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="15"/>
+        <v>5.8098705E-2</v>
+      </c>
+      <c r="K34">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="16"/>
+        <v>7.4097028434204424E-6</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="17"/>
+        <v>3.7630799738254783E-2</v>
+      </c>
+      <c r="N34" t="s">
+        <v>345</v>
+      </c>
+      <c r="O34" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>21.5</v>
+      </c>
+      <c r="B35">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>282</v>
+      </c>
+      <c r="F35" t="s">
+        <v>260</v>
+      </c>
+      <c r="G35">
+        <v>0.5</v>
+      </c>
+      <c r="H35">
+        <v>0.45212999999999998</v>
+      </c>
+      <c r="I35">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="J35">
+        <f t="shared" ref="J35:J36" si="18">PRODUCT(G35:I35)</f>
+        <v>5.8098705E-2</v>
+      </c>
+      <c r="K35">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L35">
+        <f t="shared" ref="L35:L36" si="19">K35*J35</f>
+        <v>7.4097028434204424E-6</v>
+      </c>
+      <c r="M35">
+        <f t="shared" ref="M35:M36" si="20">L35/(SUM(L$2:L$22))</f>
+        <v>3.7630799738254783E-2</v>
+      </c>
+      <c r="N35" t="s">
+        <v>341</v>
+      </c>
+      <c r="O35" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>21.5</v>
+      </c>
+      <c r="B36">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>282</v>
+      </c>
+      <c r="F36" t="s">
+        <v>260</v>
+      </c>
+      <c r="G36">
+        <v>0.5</v>
+      </c>
+      <c r="H36">
+        <v>0.45212999999999998</v>
+      </c>
+      <c r="I36">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="18"/>
+        <v>5.8098705E-2</v>
+      </c>
+      <c r="K36">
+        <v>1.27536454442839E-4</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="19"/>
+        <v>7.4097028434204424E-6</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="20"/>
+        <v>3.7630799738254783E-2</v>
+      </c>
+      <c r="N36" t="s">
+        <v>342</v>
+      </c>
+      <c r="O36" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -8188,4 +9812,10 @@
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;7&amp;K000000 Classification: In-Confidence</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d2b2326c-f811-4ccc-abcb-1b955c303c2e}" enabled="1" method="Standard" siteId="{dc781727-710e-4855-bc4c-690266a1b551}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>